--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +819,1185 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129339651</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>805565</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7364863</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129339659</v>
+      </c>
+      <c r="B4" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>805591</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7364898</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129339654</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>805651</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7365025</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>5 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129339650</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>805564</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7364858</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129339643</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>805433</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7364604</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129339649</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>805559</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7364830</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129339655</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>805591</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7364897</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129339661</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>805608</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7364899</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129339646</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>805432</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7364585</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129339653</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>805651</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7364883</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Två st. Revirhävande</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129339658</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>805589</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7364898</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129339656</v>
+      </c>
+      <c r="B14" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Livasälven, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>805570</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7364857</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,14 +1035,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1411,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,14 +1424,10 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>129339659</v>
       </c>
       <c r="B4" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129339661</v>
       </c>
       <c r="B10" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129339658</v>
       </c>
       <c r="B13" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129339656</v>
       </c>
       <c r="B14" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>129339659</v>
       </c>
       <c r="B4" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129339661</v>
       </c>
       <c r="B10" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129339658</v>
       </c>
       <c r="B13" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129339656</v>
       </c>
       <c r="B14" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>129339651</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129339659</v>
       </c>
       <c r="B4" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129339650</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129339643</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>129339649</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129339661</v>
       </c>
       <c r="B10" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129339646</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129339653</v>
       </c>
       <c r="B12" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129339658</v>
       </c>
       <c r="B13" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129339656</v>
       </c>
       <c r="B14" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>129339651</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129339659</v>
       </c>
       <c r="B4" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129339650</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129339643</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>129339649</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129339661</v>
       </c>
       <c r="B10" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129339646</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129339653</v>
       </c>
       <c r="B12" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129339658</v>
       </c>
       <c r="B13" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129339656</v>
       </c>
       <c r="B14" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>129339651</v>
       </c>
       <c r="B3" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129339659</v>
       </c>
       <c r="B4" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129339650</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129339643</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>129339649</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129339661</v>
       </c>
       <c r="B10" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>129339646</v>
       </c>
       <c r="B11" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>129339653</v>
       </c>
       <c r="B12" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129339658</v>
       </c>
       <c r="B13" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129339656</v>
       </c>
       <c r="B14" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50427-2025 artfynd.xlsx
+++ b/artfynd/A 50427-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>129339659</v>
       </c>
       <c r="B4" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>129339654</v>
       </c>
       <c r="B5" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>129339655</v>
       </c>
       <c r="B9" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>129339661</v>
       </c>
       <c r="B10" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>129339658</v>
       </c>
       <c r="B13" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>129339656</v>
       </c>
       <c r="B14" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
